--- a/data/trans_orig/IP1004-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1004-Estudios-trans_orig.xlsx
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81757</t>
+          <t>81346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86183</t>
+          <t>86177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172223</t>
+          <t>172271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177046</t>
+          <t>177712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412410</t>
+          <t>412420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472721</t>
+          <t>472524</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887444</t>
+          <t>887780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892486</t>
+          <t>892485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170300</t>
+          <t>170637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328794</t>
+          <t>328282</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>676678</t>
+          <t>676774</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>714773</t>
+          <t>713980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720782</t>
+          <t>720684</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393087</t>
+          <t>1393697</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1400982</t>
+          <t>1400942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77724</t>
+          <t>79294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170637</t>
+          <t>171115</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488750</t>
+          <t>488807</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937809</t>
+          <t>937836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>161304</t>
+          <t>161456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167932</t>
+          <t>166913</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>331305</t>
+          <t>332134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>702969</t>
+          <t>701968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741013</t>
+          <t>741078</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>746754</t>
+          <t>746756</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1446648</t>
+          <t>1446609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453575</t>
+          <t>1453642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467606</t>
+          <t>467861</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956159</t>
+          <t>956161</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>699095</t>
+          <t>699595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1444861</t>
+          <t>1444503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP1004-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1004-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,84 +722,84 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6032</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2044</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5499</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>84801</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80813</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86180</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,05%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>84801</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>81346</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86177</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,65%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,67%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>263</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172271</t>
+          <t>172324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4974</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>732</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3667</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4467</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>475780</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>472017</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>415355</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>412420</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>411885</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>475780</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>472524</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1344</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887780</t>
+          <t>887337</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3429</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3439</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3749</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>173383</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>170637</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>170627</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,61%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,02%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>489</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328282</t>
+          <t>328456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7324</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4247</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4515</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7994</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>718719</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>714650</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>720691</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>679606</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>676774</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>676506</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>718719</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>713980</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>720684</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2096</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393697</t>
+          <t>1393119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1400942</t>
+          <t>1400999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>857</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4243</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4031</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4310</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82680</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78457</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>82680</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79294</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>249</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171115</t>
+          <t>171394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,92 +2668,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4196</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>744</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3597</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>491660</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>488208</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>491660</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>488807</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1355</t>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937836</t>
+          <t>937826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3884</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4663</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4648</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4767</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170784</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>167966</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164550</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>161456</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>160677</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>170784</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>166913</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>475</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>331922</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6752</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4960</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4559</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6423</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>745122</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>740749</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>746753</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>706138</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>701968</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>702369</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,89%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>745122</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>741078</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>746756</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2079</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1446609</t>
+          <t>1446582</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453642</t>
+          <t>1453637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,107 +4271,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4429</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4379</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4864</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>470930</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>467861</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>467841</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>99,06%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1407</t>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956161</t>
+          <t>956646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4727,47 +4727,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,92 +4957,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4776</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5576</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1059</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>703011</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>699595</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>698795</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2124</t>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1444503</t>
+          <t>1444390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
